--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927E47F9-6661-4322-AAA3-1BB46515C2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3261A4-FA8F-4538-99CA-A3ADA12FD485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId1"/>
+    <sheet name="FASTags" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>S.No.</t>
   </si>
@@ -58,13 +59,43 @@
   </si>
   <si>
     <t>PULWAMA</t>
+  </si>
+  <si>
+    <t>PARK+ FASTags</t>
+  </si>
+  <si>
+    <t>Barcode Start No.</t>
+  </si>
+  <si>
+    <t>Barcode End No.</t>
+  </si>
+  <si>
+    <t>Channel / Location</t>
+  </si>
+  <si>
+    <t>Tags Qty</t>
+  </si>
+  <si>
+    <t>ARENA SXR</t>
+  </si>
+  <si>
+    <t>Dated</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Anantnag</t>
+  </si>
+  <si>
+    <t>NEXA SXR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,13 +103,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -93,16 +145,166 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -138,14 +340,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E30" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E30" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:E30" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G6" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A2:G6" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -753,4 +971,148 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4">
+        <v>6070950040322900</v>
+      </c>
+      <c r="C3" s="4">
+        <v>6070950040323000</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3">
+        <v>100</v>
+      </c>
+      <c r="F3" s="5">
+        <v>45985</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4">
+        <v>6070950040323000</v>
+      </c>
+      <c r="C4" s="4">
+        <v>6070950040323100</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="3">
+        <v>100</v>
+      </c>
+      <c r="F4" s="5">
+        <v>45985</v>
+      </c>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4">
+        <v>6075290220022690</v>
+      </c>
+      <c r="C5" s="4">
+        <v>6075290220022720</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="3">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5">
+        <v>45985</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4">
+        <v>6070950040322880</v>
+      </c>
+      <c r="C6" s="4">
+        <v>6070950040322900</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3">
+        <v>20</v>
+      </c>
+      <c r="F6" s="5">
+        <v>45985</v>
+      </c>
+      <c r="G6" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3261A4-FA8F-4538-99CA-A3ADA12FD485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844AB9CD-7FE6-4F90-A93A-3E16F8184B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>S.No.</t>
   </si>
@@ -89,6 +89,9 @@
   </si>
   <si>
     <t>NEXA SXR</t>
+  </si>
+  <si>
+    <t>HILAL BHAT</t>
   </si>
 </sst>
 </file>
@@ -241,21 +244,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -287,7 +276,21 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -354,16 +357,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G6" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G6" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="A2:G6" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -712,10 +715,18 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1">
+        <v>9596011137</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">

--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844AB9CD-7FE6-4F90-A93A-3E16F8184B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278BE48D-4935-4C35-9524-52CCC9E16243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>S.No.</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t>HILAL BHAT</t>
+  </si>
+  <si>
+    <t>2 USED</t>
+  </si>
+  <si>
+    <t>UNUSED</t>
   </si>
 </sst>
 </file>
@@ -343,10 +349,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E30" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:E30" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+  <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="13">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="12"/>
     <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="11"/>
     <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="10"/>
@@ -357,10 +365,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G6" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G6" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G18" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:G18" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="6">
+      <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="3"/>
@@ -669,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.140625" customWidth="1"/>
@@ -696,6 +706,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
+        <f>ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -713,6 +724,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <f t="shared" ref="A3:A31" si="0">ROW()-1</f>
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -730,6 +742,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="1"/>
@@ -739,6 +752,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="1"/>
@@ -748,6 +762,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="1"/>
@@ -757,6 +772,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="1"/>
@@ -766,6 +782,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="1"/>
@@ -775,6 +792,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="1"/>
@@ -784,6 +802,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="1"/>
@@ -793,6 +812,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="1"/>
@@ -802,6 +822,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="1"/>
@@ -811,6 +832,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="1"/>
@@ -820,6 +842,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="1"/>
@@ -829,6 +852,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="1"/>
@@ -838,6 +862,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="1"/>
@@ -847,6 +872,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="1"/>
@@ -856,6 +882,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="1"/>
@@ -865,6 +892,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="1"/>
@@ -874,6 +902,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="1"/>
@@ -883,6 +912,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="1"/>
@@ -892,6 +922,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="1"/>
@@ -901,6 +932,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="1"/>
@@ -910,6 +942,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="1"/>
@@ -919,6 +952,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="1"/>
@@ -928,6 +962,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="1"/>
@@ -937,6 +972,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="1"/>
@@ -946,6 +982,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="1"/>
@@ -955,6 +992,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="1"/>
@@ -964,12 +1002,23 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -986,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1034,6 +1083,7 @@
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
+        <f>ROW()-2</f>
         <v>1</v>
       </c>
       <c r="B3" s="4">
@@ -1055,6 +1105,7 @@
     </row>
     <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
+        <f t="shared" ref="A4:A18" si="0">ROW()-2</f>
         <v>2</v>
       </c>
       <c r="B4" s="4">
@@ -1076,6 +1127,7 @@
     </row>
     <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B5" s="4">
@@ -1093,10 +1145,13 @@
       <c r="F5" s="5">
         <v>45985</v>
       </c>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B6" s="4">
@@ -1114,7 +1169,163 @@
       <c r="F6" s="5">
         <v>45985</v>
       </c>
-      <c r="G6" s="3"/>
+      <c r="G6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="4">
+        <v>6070950040323100</v>
+      </c>
+      <c r="C7" s="4">
+        <v>6070950040323200</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="3">
+        <v>100</v>
+      </c>
+      <c r="F7" s="5">
+        <v>45986</v>
+      </c>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278BE48D-4935-4C35-9524-52CCC9E16243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE3FD11-F3ED-414F-BE7B-A08FA9A7D9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
-    <sheet name="Contacts" sheetId="1" r:id="rId1"/>
-    <sheet name="FASTags" sheetId="2" r:id="rId2"/>
+    <sheet name="FASTags" sheetId="2" r:id="rId1"/>
+    <sheet name="Contacts" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>S.No.</t>
   </si>
@@ -98,13 +98,88 @@
   </si>
   <si>
     <t>UNUSED</t>
+  </si>
+  <si>
+    <t>25BH3543R</t>
+  </si>
+  <si>
+    <t>607095-004-0323107</t>
+  </si>
+  <si>
+    <t>ZAKIR HUSSAIN</t>
+  </si>
+  <si>
+    <t>Barcode No.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Reg Num</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Activated</t>
+  </si>
+  <si>
+    <t>607095-004-0322900</t>
+  </si>
+  <si>
+    <t>607095-004-0323000</t>
+  </si>
+  <si>
+    <t>607529-022-0022690</t>
+  </si>
+  <si>
+    <t>607095-004-0322880</t>
+  </si>
+  <si>
+    <t>607095-004-0323100</t>
+  </si>
+  <si>
+    <t>607095-004-0323200</t>
+  </si>
+  <si>
+    <t>607529-022-0022720</t>
+  </si>
+  <si>
+    <t>TAG STATUS</t>
+  </si>
+  <si>
+    <t>CHANNEL</t>
+  </si>
+  <si>
+    <t>ARENA</t>
+  </si>
+  <si>
+    <t>607095-004-0323108</t>
+  </si>
+  <si>
+    <t>UMER YAQOOB</t>
+  </si>
+  <si>
+    <t>JK04K4481</t>
+  </si>
+  <si>
+    <t>NEXA</t>
+  </si>
+  <si>
+    <t>607095-004-0323109</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,7 +196,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -154,97 +237,277 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
+  <dxfs count="26">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -260,7 +523,7 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -276,63 +539,42 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
@@ -349,34 +591,53 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
-  <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="13">
-      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="K2:Q8" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
+  <autoFilter ref="K2:Q8" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="23">
+      <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}" name="Table2" displayName="Table2" ref="A2:G18" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <autoFilter ref="A2:G18" xr:uid="{2EA62A60-EA8D-4084-B62D-130D765E6A2D}"/>
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D895DD5F-5560-4AF1-98F6-84C7CF0CAA78}" name="S.No." dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}" name="Table3" displayName="Table3" ref="A2:H16" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
+  <autoFilter ref="A2:H16" xr:uid="{CA5C59B6-CE46-4417-A1E1-57B514AE8648}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{F980782F-9663-4F3B-A4B5-72E20C146CA6}" name="S.No." dataDxfId="14">
       <calculatedColumnFormula>ROW()-2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C4BD8CC6-1DCF-46B4-9447-0D35200C9F6A}" name="Barcode Start No." dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B46DB2E9-DEA3-4BCC-AF88-DC78CE972E00}" name="Barcode End No." dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{8F1E792C-D591-45D4-9CC6-26DC7EE74461}" name="Channel / Location" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{42F3602C-20CA-409C-B4D2-ECCE3474294B}" name="Tags Qty" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{10B0A880-1CFD-44B1-B9CD-5A12B7D02111}" name="Dated" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{39B403C8-70C4-401B-B460-C0A55C193E92}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{24379A66-65E1-4060-BC95-F052DEABD945}" name="Barcode No." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{216F9C03-A131-4460-9123-1714BC8DFA2F}" name="Name" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{4FEBDBB4-DAAA-441B-AB3A-A3A0FB7532AF}" name="Contact" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{BE80955F-5DAA-4ECC-BB79-381C74EB834B}" name="Date" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{2782C0D6-009E-4C74-8405-FDC1031A13D5}" name="Reg Num" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{F5CBE4CC-BED9-4546-922A-2AD753A3BA13}" name="CHANNEL" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{DD8A9FCE-3112-4052-BE00-322420D04B3B}" name="Status" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}" name="Table1" displayName="Table1" ref="A1:E31" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A1:E31" xr:uid="{B6DB94FA-761F-4463-AB42-A4061069BAA5}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1D31F252-7F75-4ACE-8E4E-970F96D5D0FB}" name="S.No." dataDxfId="4">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{5C2AFA5C-CFD5-43A7-83E2-31A9A1E8AA6E}" name="NAME" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{194B191E-FB6F-4E26-9A5A-32D004AC4649}" name="DESIGNATION" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{C758F67A-2E84-46C0-BF1E-17717F5D79AC}" name="CONTACT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{6C0116B5-2941-4E11-AD47-2ECED03BE947}" name="LOCATION" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -678,6 +939,440 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
+  <dimension ref="A1:Y16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.42578125" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34" style="2" customWidth="1"/>
+    <col min="14" max="14" width="31" customWidth="1"/>
+    <col min="15" max="15" width="21.7109375" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" customWidth="1"/>
+    <col min="17" max="17" width="25.5703125" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" customWidth="1"/>
+    <col min="20" max="20" width="26.85546875" customWidth="1"/>
+    <col min="21" max="21" width="17.140625" customWidth="1"/>
+    <col min="22" max="22" width="25.140625" customWidth="1"/>
+    <col min="23" max="25" width="15.5703125" style="3" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="K1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+    </row>
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <f t="shared" ref="A3:A16" si="0">ROW()-2</f>
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="4">
+        <v>6005348991</v>
+      </c>
+      <c r="E3" s="5">
+        <v>45988.500694444447</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="4">
+        <f>ROW()-2</f>
+        <v>1</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O3" s="4">
+        <v>100</v>
+      </c>
+      <c r="P3" s="5">
+        <v>45985</v>
+      </c>
+      <c r="Q3" s="4"/>
+    </row>
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="4">
+        <v>9149776065</v>
+      </c>
+      <c r="E4" s="5">
+        <v>45988</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="K4" s="4">
+        <f t="shared" ref="K4:K8" si="1">ROW()-2</f>
+        <v>2</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="4">
+        <v>100</v>
+      </c>
+      <c r="P4" s="5">
+        <v>45985</v>
+      </c>
+      <c r="Q4" s="4"/>
+    </row>
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="K5" s="4">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" s="4">
+        <v>30</v>
+      </c>
+      <c r="P5" s="5">
+        <v>45985</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="K6" s="4">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" s="4">
+        <v>20</v>
+      </c>
+      <c r="P6" s="5">
+        <v>45985</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="K7" s="4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" s="4">
+        <v>100</v>
+      </c>
+      <c r="P7" s="5">
+        <v>45986</v>
+      </c>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="K8" s="4">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K1:Q1"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4093ECB5-009B-4A95-948D-B5418A73B4F4}">
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1031,310 +1726,4 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7916C5D2-EBF3-44BC-AD33-13F607DA9441}">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <f>ROW()-2</f>
-        <v>1</v>
-      </c>
-      <c r="B3" s="4">
-        <v>6070950040322900</v>
-      </c>
-      <c r="C3" s="4">
-        <v>6070950040323000</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3">
-        <v>100</v>
-      </c>
-      <c r="F3" s="5">
-        <v>45985</v>
-      </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <f t="shared" ref="A4:A18" si="0">ROW()-2</f>
-        <v>2</v>
-      </c>
-      <c r="B4" s="4">
-        <v>6070950040323000</v>
-      </c>
-      <c r="C4" s="4">
-        <v>6070950040323100</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3">
-        <v>100</v>
-      </c>
-      <c r="F4" s="5">
-        <v>45985</v>
-      </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B5" s="4">
-        <v>6075290220022690</v>
-      </c>
-      <c r="C5" s="4">
-        <v>6075290220022720</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3">
-        <v>30</v>
-      </c>
-      <c r="F5" s="5">
-        <v>45985</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B6" s="4">
-        <v>6070950040322880</v>
-      </c>
-      <c r="C6" s="4">
-        <v>6070950040322900</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3">
-        <v>20</v>
-      </c>
-      <c r="F6" s="5">
-        <v>45985</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B7" s="4">
-        <v>6070950040323100</v>
-      </c>
-      <c r="C7" s="4">
-        <v>6070950040323200</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="3">
-        <v>100</v>
-      </c>
-      <c r="F7" s="5">
-        <v>45986</v>
-      </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-    </row>
-    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE3FD11-F3ED-414F-BE7B-A08FA9A7D9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EE885A-50D9-471B-96DB-2D784CDCD366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="FASTags" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>S.No.</t>
   </si>
@@ -173,6 +173,15 @@
   </si>
   <si>
     <t>607095-004-0323109</t>
+  </si>
+  <si>
+    <t>IQBAL SHOPIAN</t>
+  </si>
+  <si>
+    <t>SHOPIAN</t>
+  </si>
+  <si>
+    <t>RM</t>
   </si>
 </sst>
 </file>
@@ -1440,10 +1449,18 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="1">
+        <v>7006255857</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">

--- a/Contacts.xlsx
+++ b/Contacts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EE885A-50D9-471B-96DB-2D784CDCD366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13E0D1EB-3F56-49C1-B6BB-2366B852F145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3B4A4B74-8526-405E-95DA-3922D64EB034}"/>
   </bookViews>
   <sheets>
     <sheet name="FASTags" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
   <si>
     <t>S.No.</t>
   </si>
@@ -182,6 +182,15 @@
   </si>
   <si>
     <t>RM</t>
+  </si>
+  <si>
+    <t>SENT - MAQSOOD / 7006720176</t>
+  </si>
+  <si>
+    <t>607095-004-0345951</t>
+  </si>
+  <si>
+    <t>607095-004-0345960</t>
   </si>
 </sst>
 </file>
@@ -966,7 +975,7 @@
     <col min="14" max="14" width="31" customWidth="1"/>
     <col min="15" max="15" width="21.7109375" customWidth="1"/>
     <col min="16" max="16" width="21.42578125" customWidth="1"/>
-    <col min="17" max="17" width="25.5703125" customWidth="1"/>
+    <col min="17" max="17" width="35.28515625" customWidth="1"/>
     <col min="19" max="19" width="10.28515625" customWidth="1"/>
     <col min="20" max="20" width="26.85546875" customWidth="1"/>
     <col min="21" max="21" width="17.140625" customWidth="1"/>
@@ -1256,12 +1265,22 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="4"/>
+      <c r="L8" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
+      <c r="P8" s="5">
+        <v>46013</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
